--- a/scripts/fixtures/conciliacion.xlsx
+++ b/scripts/fixtures/conciliacion.xlsx
@@ -76,7 +76,7 @@
     <t>Valor a pagar</t>
   </si>
   <si>
-    <t>CUFE</t>
+    <t>CUFE / Ref</t>
   </si>
   <si>
     <t>2026-08-01</t>
@@ -1085,6 +1085,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>